--- a/results/Int Task Remove ACC -0.0/Linea_fi_explain.xlsx
+++ b/results/Int Task Remove ACC -0.0/Linea_fi_explain.xlsx
@@ -1157,7 +1157,7 @@
         <v>0.00338897652612028</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03879167024672403</v>
+        <v>0.0387885754649722</v>
       </c>
       <c r="F3" t="n">
         <v>-8.735423440433094e-05</v>
@@ -1169,10 +1169,10 @@
         <v>0.002628032102039319</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0001007330927551198</v>
+        <v>0.0001010650924521683</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0302757381067948</v>
+        <v>0.03026554807776227</v>
       </c>
       <c r="K3" t="n">
         <v>0.01629410264408711</v>
@@ -1187,7 +1187,7 @@
         <v>0.04498618441252088</v>
       </c>
       <c r="O3" t="n">
-        <v>0.03620717944049728</v>
+        <v>0.03620023258394987</v>
       </c>
       <c r="P3" t="n">
         <v>0.01319942979781769</v>
@@ -1196,7 +1196,7 @@
         <v>0.01267398959662088</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01633353390051316</v>
+        <v>0.01633689073166456</v>
       </c>
       <c r="S3" t="n">
         <v>0.3066068174941045</v>
@@ -1208,7 +1208,7 @@
         <v>0.1405073217499744</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0001047881006427864</v>
+        <v>9.784124409537353e-05</v>
       </c>
       <c r="W3" t="n">
         <v>0.005268186171651557</v>
@@ -1232,13 +1232,13 @@
         <v>0.02615899736630558</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.1407291511719673</v>
+        <v>0.1407326113795798</v>
       </c>
       <c r="AE3" t="n">
         <v>0.2452547444913009</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.1037177748245544</v>
+        <v>0.103714417993403</v>
       </c>
       <c r="AG3" t="n">
         <v>0.1472003056484424</v>
@@ -1289,7 +1289,7 @@
         <v>0.005483019343395884</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0.01217213560541979</v>
+        <v>-0.01217585861361041</v>
       </c>
       <c r="AX3" t="n">
         <v>0.0008263363404810351</v>
@@ -1316,7 +1316,7 @@
         <v>-0.001369956828058334</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.01685040556545169</v>
+        <v>0.01685376239660309</v>
       </c>
       <c r="BG3" t="n">
         <v>-0.00329949925873216</v>
@@ -1328,7 +1328,7 @@
         <v>-0.00161095834070894</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.0201948058107417</v>
+        <v>0.02019832198514395</v>
       </c>
       <c r="BK3" t="n">
         <v>0.005669251035476916</v>
@@ -1355,7 +1355,7 @@
         <v>0.0002068279274937477</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.002672965527136377</v>
+        <v>0.002669608695984984</v>
       </c>
       <c r="BT3" t="n">
         <v>-6.615088688197272e-05</v>
@@ -1373,7 +1373,7 @@
         <v>3.124666976829004e-05</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.303361427299476e-05</v>
+        <v>9.517439870744267e-06</v>
       </c>
       <c r="BZ3" t="n">
         <v>9.517439870744267e-06</v>
@@ -1385,7 +1385,7 @@
         <v>0.001160640456139311</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.00241502872594804</v>
+        <v>0.002414531524209034</v>
       </c>
       <c r="CD3" t="n">
         <v>0.0008345706167877994</v>
@@ -1428,7 +1428,7 @@
         <v>0.03364864650668301</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01854953346724183</v>
+        <v>0.01854611797014225</v>
       </c>
       <c r="F4" t="n">
         <v>0.004448827737641305</v>
@@ -1440,10 +1440,10 @@
         <v>0.006316222580656178</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001073846940767565</v>
+        <v>0.001074806881708164</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02253763995160418</v>
+        <v>0.0225402781969062</v>
       </c>
       <c r="K4" t="n">
         <v>0.0133125361207235</v>
@@ -1458,7 +1458,7 @@
         <v>0.032004282011244</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01920129924665417</v>
+        <v>0.01920059138354938</v>
       </c>
       <c r="P4" t="n">
         <v>0.02216815403531382</v>
@@ -1467,7 +1467,7 @@
         <v>0.01800579868648573</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01539985838775985</v>
+        <v>0.01539484022956602</v>
       </c>
       <c r="S4" t="n">
         <v>0.07986670257693829</v>
@@ -1479,7 +1479,7 @@
         <v>0.07772692661723654</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001076057845534983</v>
+        <v>0.001080512685728087</v>
       </c>
       <c r="W4" t="n">
         <v>0.0226980920559693</v>
@@ -1503,13 +1503,13 @@
         <v>0.04427205845936472</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.1028770416615047</v>
+        <v>0.1028799684690128</v>
       </c>
       <c r="AE4" t="n">
         <v>0.1318813221111053</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.09461282682478973</v>
+        <v>0.0946104133174817</v>
       </c>
       <c r="AG4" t="n">
         <v>0.04080448252753417</v>
@@ -1560,7 +1560,7 @@
         <v>0.01455977283100923</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.01486286702734204</v>
+        <v>0.01485972189939404</v>
       </c>
       <c r="AX4" t="n">
         <v>0.002336295602907625</v>
@@ -1587,7 +1587,7 @@
         <v>0.003322091432610942</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.02551479390366661</v>
+        <v>0.0255129707372134</v>
       </c>
       <c r="BG4" t="n">
         <v>0.02143827032140903</v>
@@ -1599,7 +1599,7 @@
         <v>0.003864418847139255</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.03694448479670693</v>
+        <v>0.03694439224616412</v>
       </c>
       <c r="BK4" t="n">
         <v>0.02677090788368732</v>
@@ -1626,7 +1626,7 @@
         <v>0.01536587072470387</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.00440779256989466</v>
+        <v>0.004408930829795378</v>
       </c>
       <c r="BT4" t="n">
         <v>0.001306258647088144</v>
@@ -1644,7 +1644,7 @@
         <v>0.0001500518370478303</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.0009013036528260542</v>
+        <v>0.0008957724155445172</v>
       </c>
       <c r="BZ4" t="n">
         <v>0.0008957724155445172</v>
@@ -1656,7 +1656,7 @@
         <v>0.003660481552416538</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.003956298003320621</v>
+        <v>0.003968688354727795</v>
       </c>
       <c r="CD4" t="n">
         <v>0.008647270639061832</v>
@@ -1738,7 +1738,7 @@
         <v>-0.008978126020241617</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.004397448808324944</v>
+        <v>-0.004363880496811012</v>
       </c>
       <c r="S5" t="n">
         <v>0.1729709605361131</v>
@@ -1927,7 +1927,7 @@
         <v>-0.000547195622435026</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0.001898734177215233</v>
+        <v>-0.001935964259121414</v>
       </c>
       <c r="CD5" t="n">
         <v>-0.004258064516129001</v>
@@ -1970,7 +1970,7 @@
         <v>-0.01289519781933447</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0260210093545838</v>
+        <v>0.02602940143246228</v>
       </c>
       <c r="F6" t="n">
         <v>-0.00103141183325883</v>
@@ -1982,7 +1982,7 @@
         <v>-0.001407306861822227</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0006178817965259015</v>
+        <v>-0.0006330962772339383</v>
       </c>
       <c r="J6" t="n">
         <v>0.01292836777272129</v>
@@ -2000,7 +2000,7 @@
         <v>0.02878228856522091</v>
       </c>
       <c r="O6" t="n">
-        <v>0.02236084109207893</v>
+        <v>0.02235215752139466</v>
       </c>
       <c r="P6" t="n">
         <v>-0.008622007272717537</v>
@@ -2253,10 +2253,10 @@
         <v>-0.0001575377175328907</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0003804734411030353</v>
+        <v>-0.0003457391583659708</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03301239237144928</v>
+        <v>0.03297819264504707</v>
       </c>
       <c r="K7" t="n">
         <v>0.01459962832860149</v>
@@ -2271,7 +2271,7 @@
         <v>0.04481593394129126</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04148438731808865</v>
+        <v>0.04146702017672011</v>
       </c>
       <c r="P7" t="n">
         <v>0.01586562373770554</v>
@@ -2292,7 +2292,7 @@
         <v>0.1269519072749339</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.0003457391583659708</v>
+        <v>-0.0003804734411030353</v>
       </c>
       <c r="W7" t="n">
         <v>0.005405150891331917</v>
@@ -2400,7 +2400,7 @@
         <v>-0.0005017534990995332</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.007431598251141498</v>
+        <v>0.007448382406898463</v>
       </c>
       <c r="BG7" t="n">
         <v>-0.003243099828039142</v>
@@ -2412,7 +2412,7 @@
         <v>-0.001103397427474356</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.01814443086338877</v>
+        <v>0.01816201173540002</v>
       </c>
       <c r="BK7" t="n">
         <v>-0.001972831817737236</v>
@@ -2439,7 +2439,7 @@
         <v>-0.003436013415118444</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.002077835991178773</v>
+        <v>0.002061051835421807</v>
       </c>
       <c r="BT7" t="n">
         <v>-0.0001080284753262939</v>
@@ -2512,7 +2512,7 @@
         <v>0.01395241329921122</v>
       </c>
       <c r="E8" t="n">
-        <v>0.05120817880312386</v>
+        <v>0.05119204977086579</v>
       </c>
       <c r="F8" t="n">
         <v>0.001798697790025428</v>
@@ -2644,7 +2644,7 @@
         <v>0.003763143207947339</v>
       </c>
       <c r="AW8" t="n">
-        <v>-0.001605326976871185</v>
+        <v>-0.001633249538300821</v>
       </c>
       <c r="AX8" t="n">
         <v>0.002317134786184563</v>
@@ -3011,7 +3011,7 @@
         <v>0.01154749916079223</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.01109677419354845</v>
+        <v>0.01112903225806458</v>
       </c>
       <c r="CD9" t="n">
         <v>0.02486969471332834</v>
